--- a/outputs/01a13eeb-3279-70e1-91ae-7e91e0c8bd97/vishu-study-schedule.xlsx
+++ b/outputs/01a13eeb-3279-70e1-91ae-7e91e0c8bd97/vishu-study-schedule.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Study schedule" sheetId="1" r:id="R400d76646dcb4bb3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Study schedule" sheetId="1" r:id="Rd5ad8a53037146b5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -50,12 +50,22 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="6">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF244C3E"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2E7"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -80,7 +90,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="15">
+  <x:cellXfs count="20">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -108,6 +118,17 @@
       <x:alignment vertical="top"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -317,6 +338,8 @@
     <x:col min="3" max="3" width="33" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="96" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="44" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="42" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -376,6 +399,12 @@
       <x:c r="E6" s="7" t="str">
         <x:v>Quiz / review</x:v>
       </x:c>
+      <x:c r="F6" s="17" t="str">
+        <x:v>Aptitude subtask</x:v>
+      </x:c>
+      <x:c r="G6" s="17" t="str">
+        <x:v>Aptitude pages</x:v>
+      </x:c>
     </x:row>
     <x:row r="7" ht="56" customHeight="1">
       <x:c r="A7" s="9" t="d">
@@ -391,10 +420,16 @@
         <x:v>Electron Transport &amp; Oxidative Phosphorylation; Pentose Phosphate Pathway; Photosynthesis - Light and Dark Reactions; remaining gaps: biomolecule structures, pH/buffers, protein folding and nucleic acid conformations</x:v>
       </x:c>
       <x:c r="E7" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="34" customHeight="1">
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F7" s="11" t="str">
+        <x:v>Number Systems · Part 1/2</x:v>
+      </x:c>
+      <x:c r="G7" s="11" t="str">
+        <x:v>1–6</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="48" customHeight="1">
       <x:c r="A8" s="12" t="d">
         <x:v>2026-10-24T00:00:00.000Z</x:v>
       </x:c>
@@ -410,8 +445,14 @@
       <x:c r="E8" s="14" t="str">
         <x:v>Full PYQ + analysis; keep existing paper</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9" ht="34" customHeight="1">
+      <x:c r="F8" s="19" t="str">
+        <x:v>Number Systems · Part 2/2</x:v>
+      </x:c>
+      <x:c r="G8" s="19" t="str">
+        <x:v>7–12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="48" customHeight="1">
       <x:c r="A9" s="12" t="d">
         <x:v>2026-10-25T00:00:00.000Z</x:v>
       </x:c>
@@ -426,6 +467,12 @@
       </x:c>
       <x:c r="E9" s="14" t="str">
         <x:v>Paid mock + analysis</x:v>
+      </x:c>
+      <x:c r="F9" s="19" t="str">
+        <x:v>Average · Part 1/1</x:v>
+      </x:c>
+      <x:c r="G9" s="19" t="str">
+        <x:v>13–18</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="56" customHeight="1">
@@ -442,7 +489,13 @@
         <x:v>Membranes, cell walls, transport, ion channels and electrical properties; organelles, protein sorting, cytoskeleton and motility</x:v>
       </x:c>
       <x:c r="E10" s="11" t="str">
-        <x:v>Weekly mistakes retry + 20 min Part A</x:v>
+        <x:v>Weekly mistakes retry</x:v>
+      </x:c>
+      <x:c r="F10" s="11" t="str">
+        <x:v>Alligation or Mixture · Part 1/1</x:v>
+      </x:c>
+      <x:c r="G10" s="11" t="str">
+        <x:v>19–24</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="56" customHeight="1">
@@ -459,7 +512,13 @@
         <x:v>Chromatin, chromosomes and transposons; cell division and cycle control; apoptosis, necrosis, autophagy; microbial growth, stress and antimicrobial resistance</x:v>
       </x:c>
       <x:c r="E11" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F11" s="11" t="str">
+        <x:v>Progressions · Part 1/2</x:v>
+      </x:c>
+      <x:c r="G11" s="11" t="str">
+        <x:v>25–29</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="56" customHeight="1">
@@ -476,7 +535,13 @@
         <x:v>DNA replication, fidelity, extrachromosomal replicons, DNA damage and repair; homologous and site-specific recombination</x:v>
       </x:c>
       <x:c r="E12" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F12" s="11" t="str">
+        <x:v>Progressions · Part 2/2</x:v>
+      </x:c>
+      <x:c r="G12" s="11" t="str">
+        <x:v>30–34</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="56" customHeight="1">
@@ -493,7 +558,13 @@
         <x:v>Transcription machinery and regulation; RNA capping, splicing, editing, polyadenylation and transport; ribozymes, riboswitches and non-coding RNA</x:v>
       </x:c>
       <x:c r="E13" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F13" s="11" t="str">
+        <x:v>Surds and Algorithm · Part 1/2</x:v>
+      </x:c>
+      <x:c r="G13" s="11" t="str">
+        <x:v>35–38</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="56" customHeight="1">
@@ -510,10 +581,16 @@
         <x:v>Genetic code and translation; inhibitors, protein modification, trafficking and degradation; phage, viral, prokaryotic and eukaryotic gene regulation; epigenetics</x:v>
       </x:c>
       <x:c r="E14" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="34" customHeight="1">
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F14" s="11" t="str">
+        <x:v>Surds and Algorithm · Part 2/2</x:v>
+      </x:c>
+      <x:c r="G14" s="11" t="str">
+        <x:v>39–42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="48" customHeight="1">
       <x:c r="A15" s="12" t="d">
         <x:v>2026-10-31T00:00:00.000Z</x:v>
       </x:c>
@@ -529,8 +606,14 @@
       <x:c r="E15" s="14" t="str">
         <x:v>Full PYQ + analysis; keep existing paper</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16" ht="34" customHeight="1">
+      <x:c r="F15" s="19" t="str">
+        <x:v>Percentage and Discount · Part 1/3</x:v>
+      </x:c>
+      <x:c r="G15" s="19" t="str">
+        <x:v>43–47</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="48" customHeight="1">
       <x:c r="A16" s="12" t="d">
         <x:v>2026-11-01T00:00:00.000Z</x:v>
       </x:c>
@@ -545,6 +628,12 @@
       </x:c>
       <x:c r="E16" s="14" t="str">
         <x:v>Paid mock + analysis</x:v>
+      </x:c>
+      <x:c r="F16" s="19" t="str">
+        <x:v>Percentage and Discount · Part 2/3</x:v>
+      </x:c>
+      <x:c r="G16" s="19" t="str">
+        <x:v>48–51</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="56" customHeight="1">
@@ -561,7 +650,13 @@
         <x:v>Receptors, hormones, GPCRs and second messengers; plant and bacterial signaling, chemotaxis and quorum sensing; adhesion, ECM, junctions and neurotransmission</x:v>
       </x:c>
       <x:c r="E17" s="11" t="str">
-        <x:v>Weekly mistakes retry + 20 min Part A</x:v>
+        <x:v>Weekly mistakes retry</x:v>
+      </x:c>
+      <x:c r="F17" s="11" t="str">
+        <x:v>Percentage and Discount · Part 3/3</x:v>
+      </x:c>
+      <x:c r="G17" s="11" t="str">
+        <x:v>52–55</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="56" customHeight="1">
@@ -578,7 +673,13 @@
         <x:v>Innate and adaptive immunity; antigens, antibodies and antibody diversity; MHC and antigen presentation; B/T-cell development, receptors and effector responses</x:v>
       </x:c>
       <x:c r="E18" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F18" s="11" t="str">
+        <x:v>Distance, Trains and Boats · Part 1/2</x:v>
+      </x:c>
+      <x:c r="G18" s="11" t="str">
+        <x:v>56–61</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="56" customHeight="1">
@@ -595,7 +696,13 @@
         <x:v>Complement, cytokines, inflammation, hypersensitivity, autoimmunity and immunodeficiency; vaccines and transplantation; host-pathogen interactions, oncogenes, tumor suppressors and cancer</x:v>
       </x:c>
       <x:c r="E19" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F19" s="11" t="str">
+        <x:v>Distance, Trains and Boats · Part 2/2</x:v>
+      </x:c>
+      <x:c r="G19" s="11" t="str">
+        <x:v>62–66</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="56" customHeight="1">
@@ -612,7 +719,13 @@
         <x:v>Potency, specification, induction, cell fate, stem cells and imprinting; animal gametogenesis, fertilization and germ layers; model-organism patterning, organogenesis, regeneration and sex determination</x:v>
       </x:c>
       <x:c r="E20" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F20" s="11" t="str">
+        <x:v>Work, Pipe and Cistern · Part 1/2</x:v>
+      </x:c>
+      <x:c r="G20" s="11" t="str">
+        <x:v>67–72</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="56" customHeight="1">
@@ -629,10 +742,16 @@
         <x:v>Plant gametogenesis, double fertilization, embryo/endosperm and germination; meristems, roots, shoots, phyllotaxy and flowering; metamorphosis, programmed cell death, aging and senescence</x:v>
       </x:c>
       <x:c r="E21" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" ht="34" customHeight="1">
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F21" s="11" t="str">
+        <x:v>Work, Pipe and Cistern · Part 2/2</x:v>
+      </x:c>
+      <x:c r="G21" s="11" t="str">
+        <x:v>73–78</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="48" customHeight="1">
       <x:c r="A22" s="12" t="d">
         <x:v>2026-11-07T00:00:00.000Z</x:v>
       </x:c>
@@ -648,8 +767,14 @@
       <x:c r="E22" s="14" t="str">
         <x:v>Full PYQ + analysis; keep existing paper</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23" ht="34" customHeight="1">
+      <x:c r="F22" s="19" t="str">
+        <x:v>Mensuration &amp; area of plane figures · Part 1/2</x:v>
+      </x:c>
+      <x:c r="G22" s="19" t="str">
+        <x:v>79–83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="48" customHeight="1">
       <x:c r="A23" s="12" t="d">
         <x:v>2026-11-08T00:00:00.000Z</x:v>
       </x:c>
@@ -664,6 +789,12 @@
       </x:c>
       <x:c r="E23" s="14" t="str">
         <x:v>Paid mock + analysis</x:v>
+      </x:c>
+      <x:c r="F23" s="19" t="str">
+        <x:v>Mensuration &amp; area of plane figures · Part 2/2</x:v>
+      </x:c>
+      <x:c r="G23" s="19" t="str">
+        <x:v>84–88</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="56" customHeight="1">
@@ -680,7 +811,13 @@
         <x:v>Photosystems, photoprotection, C3/C4/CAM and photorespiration; plant respiration and alternate oxidase; nitrogen assimilation and biological nitrogen fixation</x:v>
       </x:c>
       <x:c r="E24" s="11" t="str">
-        <x:v>Weekly mistakes retry + 20 min Part A</x:v>
+        <x:v>Weekly mistakes retry</x:v>
+      </x:c>
+      <x:c r="F24" s="11" t="str">
+        <x:v>Volume &amp; surface area of solid figures · Part 1/1</x:v>
+      </x:c>
+      <x:c r="G24" s="11" t="str">
+        <x:v>89–92</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="56" customHeight="1">
@@ -697,7 +834,13 @@
         <x:v>Plant hormone synthesis and action; phytochromes, cryptochromes and phototropins; stomata, photoperiodism, biological clocks and flowering responses</x:v>
       </x:c>
       <x:c r="E25" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F25" s="11" t="str">
+        <x:v>Geometry · Part 1/2</x:v>
+      </x:c>
+      <x:c r="G25" s="11" t="str">
+        <x:v>93–98</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="56" customHeight="1">
@@ -714,7 +857,13 @@
         <x:v>Water, mineral and solute transport; xylem, phloem and transpiration; secondary metabolites and metabolic engineering; biotic/abiotic stress and plant immunity</x:v>
       </x:c>
       <x:c r="E26" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F26" s="11" t="str">
+        <x:v>Geometry · Part 2/2</x:v>
+      </x:c>
+      <x:c r="G26" s="11" t="str">
+        <x:v>99–103</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="56" customHeight="1">
@@ -731,7 +880,13 @@
         <x:v>Blood, haemostasis and circulation; heart, ECG and blood-pressure control; respiration, gas transport and regulation; digestion, absorption, energy balance and BMR</x:v>
       </x:c>
       <x:c r="E27" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F27" s="11" t="str">
+        <x:v>Height and Distance · Part 1/1</x:v>
+      </x:c>
+      <x:c r="G27" s="11" t="str">
+        <x:v>104–107</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="56" customHeight="1">
@@ -748,10 +903,16 @@
         <x:v>Neurons, action potentials, CNS/PNS, muscle and posture; vision, hearing and touch; kidney, urine formation, osmoregulation, electrolytes and acid-base balance</x:v>
       </x:c>
       <x:c r="E28" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" ht="34" customHeight="1">
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F28" s="11" t="str">
+        <x:v>Venn Diagram · Part 1/1</x:v>
+      </x:c>
+      <x:c r="G28" s="11" t="str">
+        <x:v>108–110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="48" customHeight="1">
       <x:c r="A29" s="12" t="d">
         <x:v>2026-11-14T00:00:00.000Z</x:v>
       </x:c>
@@ -767,8 +928,14 @@
       <x:c r="E29" s="14" t="str">
         <x:v>Full PYQ + analysis; keep existing paper</x:v>
       </x:c>
-    </x:row>
-    <x:row r="30" ht="34" customHeight="1">
+      <x:c r="F29" s="19" t="str">
+        <x:v>Permutation and Combinations · Part 1/2</x:v>
+      </x:c>
+      <x:c r="G29" s="19" t="str">
+        <x:v>111–115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="48" customHeight="1">
       <x:c r="A30" s="12" t="d">
         <x:v>2026-11-15T00:00:00.000Z</x:v>
       </x:c>
@@ -783,6 +950,12 @@
       </x:c>
       <x:c r="E30" s="14" t="str">
         <x:v>Paid mock + analysis</x:v>
+      </x:c>
+      <x:c r="F30" s="19" t="str">
+        <x:v>Permutation and Combinations · Part 2/2</x:v>
+      </x:c>
+      <x:c r="G30" s="19" t="str">
+        <x:v>116–119</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="56" customHeight="1">
@@ -799,7 +972,13 @@
         <x:v>Endocrinology and reproduction; thermoregulation, stress and adaptation; gut microbiome, holobionts, gut-brain axis and dysbiosis; interorgan communication and metabolic disorders</x:v>
       </x:c>
       <x:c r="E31" s="11" t="str">
-        <x:v>Weekly mistakes retry + 20 min Part A</x:v>
+        <x:v>Weekly mistakes retry</x:v>
+      </x:c>
+      <x:c r="F31" s="11" t="str">
+        <x:v>Probability · Part 1/3</x:v>
+      </x:c>
+      <x:c r="G31" s="11" t="str">
+        <x:v>120–124</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="56" customHeight="1">
@@ -816,7 +995,13 @@
         <x:v>Mendelian and non-Mendelian inheritance, gene interactions and imprinting; linkage, crossing-over, tetrads and mapping; bacterial gene transfer and mapping populations</x:v>
       </x:c>
       <x:c r="E32" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F32" s="11" t="str">
+        <x:v>Probability · Part 2/3</x:v>
+      </x:c>
+      <x:c r="G32" s="11" t="str">
+        <x:v>125–128</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="56" customHeight="1">
@@ -833,7 +1018,13 @@
         <x:v>Mutation and complementation; pedigree, LOD and human genetic disorders; quantitative/polygenic inheritance, heritability and Hardy-Weinberg; chromosomal alterations and ploidy</x:v>
       </x:c>
       <x:c r="E33" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F33" s="11" t="str">
+        <x:v>Probability · Part 3/3</x:v>
+      </x:c>
+      <x:c r="G33" s="11" t="str">
+        <x:v>129–132</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="56" customHeight="1">
@@ -850,7 +1041,13 @@
         <x:v>Origin of life, multicellularity and evolutionary mechanisms; speciation, extinction, adaptive radiation, coevolution and human evolution; species concepts, taxonomy and nomenclature</x:v>
       </x:c>
       <x:c r="E34" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F34" s="11" t="str">
+        <x:v>Function and Graph · Part 1/1</x:v>
+      </x:c>
+      <x:c r="G34" s="11" t="str">
+        <x:v>133–137</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="56" customHeight="1">
@@ -867,10 +1064,16 @@
         <x:v>Bacteria, archaea and viruses; protists, algae and fungi; plant groups, morphology, anatomy and reproduction; invertebrate/vertebrate diversity and evolutionary relationships</x:v>
       </x:c>
       <x:c r="E35" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="34" customHeight="1">
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F35" s="11" t="str">
+        <x:v>Calendar, clock · Part 1/2</x:v>
+      </x:c>
+      <x:c r="G35" s="11" t="str">
+        <x:v>138–141</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="48" customHeight="1">
       <x:c r="A36" s="12" t="d">
         <x:v>2026-11-21T00:00:00.000Z</x:v>
       </x:c>
@@ -886,8 +1089,14 @@
       <x:c r="E36" s="14" t="str">
         <x:v>Full PYQ + analysis; keep existing paper</x:v>
       </x:c>
-    </x:row>
-    <x:row r="37" ht="34" customHeight="1">
+      <x:c r="F36" s="19" t="str">
+        <x:v>Calendar, clock · Part 2/2</x:v>
+      </x:c>
+      <x:c r="G36" s="19" t="str">
+        <x:v>142–144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="48" customHeight="1">
       <x:c r="A37" s="12" t="d">
         <x:v>2026-11-22T00:00:00.000Z</x:v>
       </x:c>
@@ -902,6 +1111,12 @@
       </x:c>
       <x:c r="E37" s="14" t="str">
         <x:v>Paid mock + analysis</x:v>
+      </x:c>
+      <x:c r="F37" s="19" t="str">
+        <x:v>Series &amp; missing characters · Part 1/1</x:v>
+      </x:c>
+      <x:c r="G37" s="19" t="str">
+        <x:v>145–147</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="56" customHeight="1">
@@ -918,7 +1133,13 @@
         <x:v>Ecological factors and adaptations; population models, life tables and metapopulations; species interactions, succession, food webs, productivity, energy flow and biogeochemical cycles</x:v>
       </x:c>
       <x:c r="E38" s="11" t="str">
-        <x:v>Weekly mistakes retry + 20 min Part A</x:v>
+        <x:v>Weekly mistakes retry</x:v>
+      </x:c>
+      <x:c r="F38" s="11" t="str">
+        <x:v>Syllogism · Part 1/1</x:v>
+      </x:c>
+      <x:c r="G38" s="11" t="str">
+        <x:v>148–149</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="56" customHeight="1">
@@ -935,7 +1156,13 @@
         <x:v>Climate change, pollution and invasive species; biodiversity, conservation, PVA, IUCN and seed banks; biodiversity/PPVFR policies; foraging, communication, migration, social and reproductive behaviour</x:v>
       </x:c>
       <x:c r="E39" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F39" s="11" t="str">
+        <x:v>Previous Year NET Solutions · Part 1/11</x:v>
+      </x:c>
+      <x:c r="G39" s="11" t="str">
+        <x:v>150–155</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="56" customHeight="1">
@@ -952,7 +1179,13 @@
         <x:v>Sequence, structure and expression databases; BLAST/FASTA, homology, scoring matrices and pairwise/multiple alignments; gene annotation, variation, comparative genomics and phylogenetics</x:v>
       </x:c>
       <x:c r="E40" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F40" s="11" t="str">
+        <x:v>Previous Year NET Solutions · Part 2/11</x:v>
+      </x:c>
+      <x:c r="G40" s="11" t="str">
+        <x:v>156–161</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="56" customHeight="1">
@@ -969,7 +1202,13 @@
         <x:v>Molecular modelling, dynamics and force fields; protein structure prediction and AlphaFold; drug design, QSAR, pharmacophores and ADMET; systems biology, data science and pathway modelling</x:v>
       </x:c>
       <x:c r="E41" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F41" s="11" t="str">
+        <x:v>Previous Year NET Solutions · Part 3/11</x:v>
+      </x:c>
+      <x:c r="G41" s="11" t="str">
+        <x:v>162–167</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="56" customHeight="1">
@@ -986,10 +1225,16 @@
         <x:v>Calculus, differential equations, linear algebra and numerical methods; material/energy balances, heat/mass/momentum transfer; biological thermodynamics, flux, entropy and coupled reactions</x:v>
       </x:c>
       <x:c r="E42" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" ht="34" customHeight="1">
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F42" s="11" t="str">
+        <x:v>Previous Year NET Solutions · Part 4/11</x:v>
+      </x:c>
+      <x:c r="G42" s="11" t="str">
+        <x:v>168–173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="48" customHeight="1">
       <x:c r="A43" s="12" t="d">
         <x:v>2026-11-28T00:00:00.000Z</x:v>
       </x:c>
@@ -1005,8 +1250,14 @@
       <x:c r="E43" s="14" t="str">
         <x:v>Full PYQ + analysis; keep existing paper</x:v>
       </x:c>
-    </x:row>
-    <x:row r="44" ht="34" customHeight="1">
+      <x:c r="F43" s="19" t="str">
+        <x:v>Previous Year NET Solutions · Part 5/11</x:v>
+      </x:c>
+      <x:c r="G43" s="19" t="str">
+        <x:v>174–179</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="48" customHeight="1">
       <x:c r="A44" s="12" t="d">
         <x:v>2026-11-29T00:00:00.000Z</x:v>
       </x:c>
@@ -1021,6 +1272,12 @@
       </x:c>
       <x:c r="E44" s="14" t="str">
         <x:v>Paid mock + analysis</x:v>
+      </x:c>
+      <x:c r="F44" s="19" t="str">
+        <x:v>Previous Year NET Solutions · Part 6/11</x:v>
+      </x:c>
+      <x:c r="G44" s="19" t="str">
+        <x:v>180–185</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="56" customHeight="1">
@@ -1037,7 +1294,13 @@
         <x:v>Microbial growth and substrate kinetics; batch, fed-batch and continuous reactors; sterilization, oxygen transfer, aeration and agitation; industrial fermentation, biotransformation and process economics</x:v>
       </x:c>
       <x:c r="E45" s="11" t="str">
-        <x:v>Weekly mistakes retry + 20 min Part A</x:v>
+        <x:v>Weekly mistakes retry</x:v>
+      </x:c>
+      <x:c r="F45" s="11" t="str">
+        <x:v>Previous Year NET Solutions · Part 7/11</x:v>
+      </x:c>
+      <x:c r="G45" s="11" t="str">
+        <x:v>186–191</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="56" customHeight="1">
@@ -1054,7 +1317,13 @@
         <x:v>Enzyme/protein engineering, immobilization and Thiele modulus; downstream recovery and purification; plant design and scale-up; metabolic engineering and synthetic biology</x:v>
       </x:c>
       <x:c r="E46" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F46" s="11" t="str">
+        <x:v>Previous Year NET Solutions · Part 8/11</x:v>
+      </x:c>
+      <x:c r="G46" s="11" t="str">
+        <x:v>192–197</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="56" customHeight="1">
@@ -1071,7 +1340,13 @@
         <x:v>Recombinant DNA, cloning, expression, mutagenesis, knockout and genome editing; sequencing and expression analysis; diagnostics, immunotherapy, vaccines, phage display and biosensors</x:v>
       </x:c>
       <x:c r="E47" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F47" s="11" t="str">
+        <x:v>Previous Year NET Solutions · Part 9/11</x:v>
+      </x:c>
+      <x:c r="G47" s="11" t="str">
+        <x:v>198–202</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="56" customHeight="1">
@@ -1088,7 +1363,13 @@
         <x:v>Stem cells, iPSCs, organoids, cell/tissue engineering and medical devices; neurobiology methods; transgenic animals, breeding and germplasm; plant tissue culture, transgenics and marker-assisted breeding</x:v>
       </x:c>
       <x:c r="E48" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F48" s="11" t="str">
+        <x:v>Previous Year NET Solutions · Part 10/11</x:v>
+      </x:c>
+      <x:c r="G48" s="11" t="str">
+        <x:v>203–207</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="56" customHeight="1">
@@ -1105,10 +1386,16 @@
         <x:v>Marine organisms and resources, marine microbes/metabolites, seafood microbiology, biofilms and oceanography; wastewater treatment, bioremediation, phytoremediation, biofertilizers, biopesticides and waste-to-biofuel</x:v>
       </x:c>
       <x:c r="E49" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" ht="34" customHeight="1">
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F49" s="11" t="str">
+        <x:v>Previous Year NET Solutions · Part 11/11</x:v>
+      </x:c>
+      <x:c r="G49" s="11" t="str">
+        <x:v>208–212</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="48" customHeight="1">
       <x:c r="A50" s="12" t="d">
         <x:v>2026-12-05T00:00:00.000Z</x:v>
       </x:c>
@@ -1124,8 +1411,14 @@
       <x:c r="E50" s="14" t="str">
         <x:v>Full PYQ + analysis; keep existing paper</x:v>
       </x:c>
-    </x:row>
-    <x:row r="51" ht="34" customHeight="1">
+      <x:c r="F50" s="19" t="str">
+        <x:v>Previous Year GATE Solutions · Part 1/6</x:v>
+      </x:c>
+      <x:c r="G50" s="19" t="str">
+        <x:v>213–218</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="48" customHeight="1">
       <x:c r="A51" s="12" t="d">
         <x:v>2026-12-06T00:00:00.000Z</x:v>
       </x:c>
@@ -1140,6 +1433,12 @@
       </x:c>
       <x:c r="E51" s="14" t="str">
         <x:v>Paid mock + analysis</x:v>
+      </x:c>
+      <x:c r="F51" s="19" t="str">
+        <x:v>Previous Year GATE Solutions · Part 2/6</x:v>
+      </x:c>
+      <x:c r="G51" s="19" t="str">
+        <x:v>219–224</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="56" customHeight="1">
@@ -1156,7 +1455,13 @@
         <x:v>Macromolecule isolation, chromatography, electrophoresis and centrifugation; UV/fluorescence/CD/NMR/ESR, X-ray, cryo-EM, mass spectrometry and SPR; genomics, transcriptomics, proteomics, metabolomics and single-cell methods</x:v>
       </x:c>
       <x:c r="E52" s="11" t="str">
-        <x:v>Weekly mistakes retry + 20 min Part A</x:v>
+        <x:v>Weekly mistakes retry</x:v>
+      </x:c>
+      <x:c r="F52" s="11" t="str">
+        <x:v>Previous Year GATE Solutions · Part 3/6</x:v>
+      </x:c>
+      <x:c r="G52" s="11" t="str">
+        <x:v>225–230</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="56" customHeight="1">
@@ -1173,7 +1478,13 @@
         <x:v>Radiolabeling and safety; ELISA, RIA, western blot, immunoprecipitation, flow cytometry, FISH/GISH; light/electron microscopy; patch clamp, brain imaging and field sampling methods</x:v>
       </x:c>
       <x:c r="E53" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F53" s="11" t="str">
+        <x:v>Previous Year GATE Solutions · Part 4/6</x:v>
+      </x:c>
+      <x:c r="G53" s="11" t="str">
+        <x:v>231–235</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="56" customHeight="1">
@@ -1190,7 +1501,13 @@
         <x:v>Accuracy, precision, probability and distributions; hypothesis testing, confidence intervals, t-test, ANOVA, chi-square, regression and multivariate basics; IPR, patents, biosafety, animal/research ethics and AI in research</x:v>
       </x:c>
       <x:c r="E54" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F54" s="11" t="str">
+        <x:v>Previous Year GATE Solutions · Part 5/6</x:v>
+      </x:c>
+      <x:c r="G54" s="11" t="str">
+        <x:v>236–240</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="34" customHeight="1">
@@ -1207,7 +1524,13 @@
         <x:v>Units 1-14: recurring wrong answers, experimental interpretation, pathway maps, bioprocess calculations, methods and formula sheets; Part A recap</x:v>
       </x:c>
       <x:c r="E55" s="11" t="str">
-        <x:v>Previous-topic quiz/review + 20 min Part A</x:v>
+        <x:v>Previous-topic quiz/review</x:v>
+      </x:c>
+      <x:c r="F55" s="11" t="str">
+        <x:v>Previous Year GATE Solutions · Part 6/6</x:v>
+      </x:c>
+      <x:c r="G55" s="11" t="str">
+        <x:v>241–245</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
